--- a/Results/Study 2/GoogLeNet/Confusion Matrices.xlsx
+++ b/Results/Study 2/GoogLeNet/Confusion Matrices.xlsx
@@ -400,10 +400,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>542</v>
+        <v>299</v>
       </c>
       <c r="C2">
-        <v>98</v>
+        <v>341</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -411,10 +411,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>115</v>
+        <v>238</v>
       </c>
       <c r="C3">
-        <v>525</v>
+        <v>402</v>
       </c>
     </row>
   </sheetData>
@@ -440,10 +440,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>114</v>
+        <v>64</v>
       </c>
       <c r="C2">
-        <v>46</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -451,10 +451,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="C3">
-        <v>130</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Study 2/GoogLeNet/Confusion Matrices.xlsx
+++ b/Results/Study 2/GoogLeNet/Confusion Matrices.xlsx
@@ -400,10 +400,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="C2">
-        <v>341</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -411,10 +411,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C3">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Study 2/GoogLeNet/Confusion Matrices.xlsx
+++ b/Results/Study 2/GoogLeNet/Confusion Matrices.xlsx
@@ -400,10 +400,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="C2">
-        <v>350</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -411,10 +411,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>242</v>
+        <v>298</v>
       </c>
       <c r="C3">
-        <v>398</v>
+        <v>342</v>
       </c>
     </row>
   </sheetData>
@@ -440,10 +440,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="C2">
-        <v>96</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -451,10 +451,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C3">
-        <v>94</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
